--- a/data/trending_integrated_20260909_11.xlsx
+++ b/data/trending_integrated_20260909_11.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29105139135</v>
+        <v>29209397555</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -619,7 +619,7 @@
         <v>2300</v>
       </c>
       <c r="R2" t="n">
-        <v>-15000</v>
+        <v>164000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -673,10 +673,10 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>36821088165</v>
+        <v>36894580185</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -711,7 +711,7 @@
         <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>84000</v>
+        <v>29000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13980</v>
+        <v>14310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.37%</t>
+          <t>+21.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>805</v>
+        <v>845</v>
       </c>
       <c r="H4" t="n">
         <v>5.64</v>
@@ -785,7 +785,7 @@
         <v>12050</v>
       </c>
       <c r="L4" t="n">
-        <v>14200</v>
+        <v>14370</v>
       </c>
       <c r="M4" t="n">
         <v>11950</v>
@@ -794,7 +794,7 @@
         <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>275769823370</v>
+        <v>306684044415</v>
       </c>
       <c r="P4" t="n">
         <v>30200</v>
@@ -803,10 +803,10 @@
         <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>553000</v>
+        <v>515000</v>
       </c>
       <c r="S4" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7280</v>
+        <v>7150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.29%</t>
+          <t>+14.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>431</v>
+        <v>519</v>
       </c>
       <c r="H5" t="n">
         <v>7.4</v>
@@ -886,7 +886,7 @@
         <v>7.35</v>
       </c>
       <c r="O5" t="n">
-        <v>42228810730</v>
+        <v>45982359535</v>
       </c>
       <c r="P5" t="n">
         <v>21500</v>
@@ -895,23 +895,23 @@
         <v>4565</v>
       </c>
       <c r="R5" t="n">
-        <v>9000</v>
+        <v>-376000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신약 개발(페니트리움바이오) 관련 희망 회로와 주가 부진에 대한 답답함 토로. 실험 결과 발표 기대.</t>
+          <t>오가노이드 및 뎅기열 관련 신규 임상 결과 발표에 따른 긍정적 전망. 항암제 개발 기대감 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약개발', '희망회로', '실험결과']</t>
+          <t>['오가노이드', '뎅기열', '항암제']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7320</v>
+        <v>54800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.84%</t>
+          <t>+11.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G6" t="n">
-        <v>171</v>
+        <v>381</v>
       </c>
       <c r="H6" t="n">
-        <v>16.71</v>
+        <v>14.96</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6430</v>
+        <v>49250</v>
       </c>
       <c r="K6" t="n">
-        <v>6400</v>
+        <v>53500</v>
       </c>
       <c r="L6" t="n">
-        <v>7470</v>
+        <v>59000</v>
       </c>
       <c r="M6" t="n">
-        <v>6250</v>
+        <v>51600</v>
       </c>
       <c r="N6" t="n">
-        <v>16.4</v>
+        <v>14.93</v>
       </c>
       <c r="O6" t="n">
-        <v>67652376605</v>
+        <v>135754430350</v>
       </c>
       <c r="P6" t="n">
-        <v>13000</v>
+        <v>108900</v>
       </c>
       <c r="Q6" t="n">
-        <v>6030</v>
+        <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>-91000</v>
+        <v>-225000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주주환원 정책 및 공매도 관련 언급, 반도체 사업 부문에 대한 저평가 주장. 외인 매도세 속 주가 상승 기대.</t>
+          <t>수소 에너지 관련 기업의 성장성 및 목표가 상향 기대. 기관 매수세 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주주환원', '공매도', '반도체']</t>
+          <t>['수소에너지', '성장성', '기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55200</v>
+        <v>7070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.08%</t>
+          <t>+9.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="F7" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
-        <v>363</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
-        <v>14.96</v>
+        <v>16.71</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49250</v>
+        <v>6430</v>
       </c>
       <c r="K7" t="n">
-        <v>53500</v>
+        <v>6400</v>
       </c>
       <c r="L7" t="n">
-        <v>59000</v>
+        <v>7470</v>
       </c>
       <c r="M7" t="n">
-        <v>51600</v>
+        <v>6250</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93</v>
+        <v>16.4</v>
       </c>
       <c r="O7" t="n">
-        <v>133186977500</v>
+        <v>73255064640</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>13000</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>6030</v>
       </c>
       <c r="R7" t="n">
-        <v>-232000</v>
+        <v>-554000</v>
       </c>
       <c r="S7" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관/외인 수급 변화 및 목표가 관련 논의. 수소 연료 전지 사업 성장성 언급.</t>
+          <t>6천억~1조 규모 주주환원 및 배당 관련 긍정적 전망. 공매도 세력에 대한 기대감 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외인', '수소연료전지']</t>
+          <t>['주주환원', '배당', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8370</v>
+        <v>8330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.98%</t>
+          <t>+8.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1.4</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H8" t="n">
         <v>1.81</v>
@@ -1162,7 +1162,7 @@
         <v>0.41</v>
       </c>
       <c r="O8" t="n">
-        <v>93016766555</v>
+        <v>94375689195</v>
       </c>
       <c r="P8" t="n">
         <v>10300</v>
@@ -1171,7 +1171,7 @@
         <v>952</v>
       </c>
       <c r="R8" t="n">
-        <v>-73000</v>
+        <v>-206000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14720</v>
+        <v>14830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.45%</t>
+          <t>+8.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>930</v>
+        <v>949</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>359062276575</v>
+        <v>364548002510</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1263,23 +1263,23 @@
         <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>559000</v>
+        <v>820000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 상승 추세 기대. 미국 광통신 종목 동반 상승 언급. 공매도 물량 소화.</t>
+          <t>단기 박스권 돌파 및 우상향 추세 전망. 공매도 물량 청산 기대감 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '상승추세', '공매도']</t>
+          <t>['상한가', '우상향', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.92%</t>
+          <t>+7.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H10" t="n">
         <v>0.51</v>
@@ -1346,7 +1346,7 @@
         <v>0.61</v>
       </c>
       <c r="O10" t="n">
-        <v>12317890385</v>
+        <v>12841113661</v>
       </c>
       <c r="P10" t="n">
         <v>2930</v>
@@ -1355,7 +1355,7 @@
         <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>29000</v>
+        <v>70000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3850</v>
+        <v>3890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2.74</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F11" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G11" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="H11" t="n">
         <v>3.19</v>
@@ -1438,7 +1438,7 @@
         <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>241763663096</v>
+        <v>245383209824</v>
       </c>
       <c r="P11" t="n">
         <v>8100</v>
@@ -1447,7 +1447,7 @@
         <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-15000</v>
+        <v>-348000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1855000</v>
+        <v>92900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>795</v>
+        <v>242</v>
       </c>
       <c r="F12" t="n">
-        <v>441</v>
+        <v>168</v>
       </c>
       <c r="G12" t="n">
-        <v>2180</v>
+        <v>1435</v>
       </c>
       <c r="H12" t="n">
-        <v>50.66</v>
+        <v>23.61</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1793000</v>
+        <v>89500</v>
       </c>
       <c r="K12" t="n">
-        <v>1795000</v>
+        <v>92000</v>
       </c>
       <c r="L12" t="n">
-        <v>1864000</v>
+        <v>94400</v>
       </c>
       <c r="M12" t="n">
-        <v>1795000</v>
+        <v>91300</v>
       </c>
       <c r="N12" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="O12" t="n">
-        <v>2643279558000</v>
+        <v>215319549150</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>277000</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>11000</v>
+        <v>104000</v>
       </c>
       <c r="S12" t="n">
-        <v>-3000</v>
+        <v>26000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국채 금리 하락과 함께 차트 분석 기반 190 돌파 및 200 이상 상승 기대감 형성. UBS 매집 및 시체 감소 언급.</t>
+          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미국채 금리', '차트 분석', 'HBM']</t>
+          <t>['원전', 'SMR', '프랑스 협력']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>92500</v>
+        <v>1859000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+3.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>236</v>
+        <v>795</v>
       </c>
       <c r="F13" t="n">
-        <v>168</v>
+        <v>445</v>
       </c>
       <c r="G13" t="n">
-        <v>1420</v>
+        <v>2194</v>
       </c>
       <c r="H13" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>92000</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>94400</v>
+        <v>1864000</v>
       </c>
       <c r="M13" t="n">
-        <v>91300</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>209388378000</v>
+        <v>2750704625000</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>113000</v>
+        <v>53000</v>
       </c>
       <c r="S13" t="n">
-        <v>15000</v>
+        <v>37000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+          <t>SK하이닉스 주가 190~200만원대 회복 및 추가 상승 전망. 자사주 매입 및 기관 매집 관련 긍정적 신호 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '프랑스 협력']</t>
+          <t>['반도체', 'HBM', '자사주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30350</v>
+        <v>30250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F14" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G14" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H14" t="n">
         <v>0.31</v>
@@ -1714,7 +1714,7 @@
         <v>0.23</v>
       </c>
       <c r="O14" t="n">
-        <v>231112094175</v>
+        <v>233706993925</v>
       </c>
       <c r="P14" t="n">
         <v>39350</v>
@@ -1723,7 +1723,7 @@
         <v>8200</v>
       </c>
       <c r="R14" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>273500</v>
+        <v>273750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>790</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G15" t="n">
-        <v>1726</v>
+        <v>1697</v>
       </c>
       <c r="H15" t="n">
         <v>46.85</v>
@@ -1797,7 +1797,7 @@
         <v>269500</v>
       </c>
       <c r="L15" t="n">
-        <v>274000</v>
+        <v>274500</v>
       </c>
       <c r="M15" t="n">
         <v>268500</v>
@@ -1806,7 +1806,7 @@
         <v>46.79</v>
       </c>
       <c r="O15" t="n">
-        <v>1701016930000</v>
+        <v>1848418750000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,14 +1815,14 @@
         <v>70000</v>
       </c>
       <c r="R15" t="n">
-        <v>-486000</v>
+        <v>-301000</v>
       </c>
       <c r="S15" t="n">
-        <v>12000</v>
+        <v>176000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 업황 및 경쟁사(하이닉스) 비교 언급. 정치적 발언 및 개인적인 매매 전략 공유.</t>
+          <t>삼성전자 주가 관련 혼조세, 하이닉스와의 비교 언급. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '하이닉스', '매매 전략']</t>
+          <t>['반도체', '주가', '하이닉스']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9050</v>
+        <v>9060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H16" t="n">
         <v>27.69</v>
@@ -1889,7 +1889,7 @@
         <v>8940</v>
       </c>
       <c r="L16" t="n">
-        <v>9060</v>
+        <v>9070</v>
       </c>
       <c r="M16" t="n">
         <v>8710</v>
@@ -1898,7 +1898,7 @@
         <v>28.05</v>
       </c>
       <c r="O16" t="n">
-        <v>15086996990</v>
+        <v>16039677820</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,10 +1907,10 @@
         <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-243000</v>
+        <v>-289000</v>
       </c>
       <c r="S16" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,27 +1947,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34500</v>
+        <v>34550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="H17" t="n">
-        <v>52.68</v>
+        <v>52.67</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>21.01</v>
       </c>
       <c r="O17" t="n">
-        <v>51319193800</v>
+        <v>52833652650</v>
       </c>
       <c r="P17" t="n">
         <v>69500</v>
@@ -1999,10 +1999,10 @@
         <v>30400</v>
       </c>
       <c r="R17" t="n">
-        <v>-26000</v>
+        <v>-78000</v>
       </c>
       <c r="S17" t="n">
-        <v>15000</v>
+        <v>61000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12100</v>
+        <v>12030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>31382019440</v>
+        <v>32362285865</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2091,10 +2091,10 @@
         <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>37000</v>
+        <v>43000</v>
       </c>
       <c r="S18" t="n">
-        <v>-3000</v>
+        <v>-6000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19790</v>
+        <v>20000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F19" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G19" t="n">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="H19" t="n">
         <v>10.85</v>
@@ -2174,7 +2174,7 @@
         <v>10.47</v>
       </c>
       <c r="O19" t="n">
-        <v>186693858625</v>
+        <v>192675664420</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2183,10 +2183,10 @@
         <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-976000</v>
+        <v>-844000</v>
       </c>
       <c r="S19" t="n">
-        <v>-23000</v>
+        <v>45000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10210</v>
+        <v>10160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.20%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.32</v>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H20" t="n">
         <v>0.9399999999999999</v>
@@ -2266,7 +2266,7 @@
         <v>0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>121468759935</v>
+        <v>123389341610</v>
       </c>
       <c r="P20" t="n">
         <v>15960</v>
@@ -2275,7 +2275,7 @@
         <v>3500</v>
       </c>
       <c r="R20" t="n">
-        <v>34000</v>
+        <v>-43000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
